--- a/Assignment.xlsx
+++ b/Assignment.xlsx
@@ -13,6 +13,9 @@
     <sheet name="Sheet3" sheetId="3" state="hidden" r:id="rId4"/>
   </sheets>
   <calcPr calcId="144525"/>
+  <pivotCaches>
+    <pivotCache cacheId="8" r:id="rId5"/>
+  </pivotCaches>
 </workbook>
 </file>
 
@@ -280,7 +283,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -423,12 +426,123 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="65"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="65"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -493,11 +607,17 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -511,6 +631,322 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Noor Computer" refreshedDate="46292.09680428241" createdVersion="4" refreshedVersion="4" minRefreshableVersion="3" recordCount="18">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A5:G23" sheet="Sheet4"/>
+  </cacheSource>
+  <cacheFields count="7">
+    <cacheField name="Sales Person" numFmtId="0">
+      <sharedItems count="18">
+        <s v="Ryan Asif"/>
+        <s v="Shayan Siddiqui"/>
+        <s v="Ahmed Dayan"/>
+        <s v="Khuzema Afridi"/>
+        <s v="Fawad Ahmed"/>
+        <s v="Talha Qadri"/>
+        <s v="Muaz Khan"/>
+        <s v="Shahid Anwar"/>
+        <s v="Bilal Ahmed"/>
+        <s v="Faizan Hashmi"/>
+        <s v="Muhammad Saffi"/>
+        <s v="Muzammil Ahmed"/>
+        <s v="Burhan Jalali"/>
+        <s v="Mukshaf Ahmed"/>
+        <s v="Tanveer Ali"/>
+        <s v="Mahad Raza"/>
+        <s v="Irfan Junejo"/>
+        <s v="Muhammad Waseem"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Region" numFmtId="0">
+      <sharedItems count="6">
+        <s v="Pakistan"/>
+        <s v="China"/>
+        <s v="Iran"/>
+        <s v="India"/>
+        <s v="Brazil"/>
+        <s v="Mexico"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Product" numFmtId="0">
+      <sharedItems count="15">
+        <s v="Shampoo"/>
+        <s v="Soap"/>
+        <s v="Sun Block"/>
+        <s v="Tyres"/>
+        <s v="Cars"/>
+        <s v="Glasses"/>
+        <s v="Phones"/>
+        <s v="Watches"/>
+        <s v="Fishes"/>
+        <s v="Boats"/>
+        <s v="Automobiles"/>
+        <s v="Equipment"/>
+        <s v="Bitcoin"/>
+        <s v="Toys"/>
+        <s v="Clothes"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Jan" numFmtId="44">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="10000450" maxValue="14543000" count="10">
+        <n v="10012000"/>
+        <n v="10013000"/>
+        <n v="10345000"/>
+        <n v="10000450"/>
+        <n v="10013400"/>
+        <n v="10034000"/>
+        <n v="10067000"/>
+        <n v="10018700"/>
+        <n v="10013340"/>
+        <n v="14543000"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Feb" numFmtId="44">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="10000450" maxValue="10345000" count="9">
+        <n v="10067000"/>
+        <n v="10013000"/>
+        <n v="10012000"/>
+        <n v="10345000"/>
+        <n v="10000450"/>
+        <n v="10034000"/>
+        <n v="10018700"/>
+        <n v="10013340"/>
+        <n v="10013400"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Mar" numFmtId="44">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="10000450" maxValue="10345000" count="9">
+        <n v="10013000"/>
+        <n v="10345000"/>
+        <n v="10034000"/>
+        <n v="10067000"/>
+        <n v="10018700"/>
+        <n v="10013340"/>
+        <n v="10000450"/>
+        <n v="10013400"/>
+        <n v="10012000"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Grand Total" numFmtId="44">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="30019600" maxValue="34901400" count="18">
+        <n v="30092000"/>
+        <n v="30371000"/>
+        <n v="30391000"/>
+        <n v="30080450"/>
+        <n v="30377100"/>
+        <n v="30047790"/>
+        <n v="30757000"/>
+        <n v="30019600"/>
+        <n v="30039740"/>
+        <n v="34901400"/>
+        <n v="30081400"/>
+        <n v="30168000"/>
+        <n v="30098700"/>
+        <n v="30038340"/>
+        <n v="30369000"/>
+        <n v="30026450"/>
+        <n v="30703400"/>
+        <n v="30034900"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="18">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="3"/>
+    <x v="4"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="5"/>
+    <x v="5"/>
+    <x v="5"/>
+    <x v="4"/>
+    <x v="5"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="0"/>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="1"/>
+    <x v="7"/>
+    <x v="7"/>
+    <x v="4"/>
+    <x v="6"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="2"/>
+    <x v="8"/>
+    <x v="8"/>
+    <x v="1"/>
+    <x v="7"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="3"/>
+    <x v="9"/>
+    <x v="9"/>
+    <x v="3"/>
+    <x v="7"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="4"/>
+    <x v="10"/>
+    <x v="4"/>
+    <x v="5"/>
+    <x v="2"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <x v="5"/>
+    <x v="11"/>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="0"/>
+    <x v="12"/>
+    <x v="6"/>
+    <x v="6"/>
+    <x v="0"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <x v="1"/>
+    <x v="13"/>
+    <x v="1"/>
+    <x v="7"/>
+    <x v="8"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <x v="2"/>
+    <x v="14"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="8"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <x v="3"/>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <x v="16"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="8"/>
+    <x v="1"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <x v="17"/>
+    <x v="5"/>
+    <x v="8"/>
+    <x v="3"/>
+    <x v="5"/>
+    <x v="6"/>
+    <x v="17"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="I5:K22" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="7">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+    <pivotField numFmtId="44" showAll="0"/>
+  </pivotFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1433,6 +1869,9 @@
       <c r="G5" s="16" t="s">
         <v>40</v>
       </c>
+      <c r="I5" s="26"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="28"/>
     </row>
     <row r="6" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
@@ -1457,27 +1896,30 @@
         <f>SUM(D6,E6,F6)</f>
         <v>30092000</v>
       </c>
-      <c r="L6" s="26"/>
-      <c r="P6" s="26"/>
-      <c r="Q6" s="26"/>
-      <c r="U6" s="26"/>
-      <c r="V6" s="26"/>
-      <c r="AB6" s="26"/>
-      <c r="AC6" s="26"/>
-      <c r="AE6" s="26"/>
-      <c r="AF6" s="26"/>
-      <c r="AJ6" s="26"/>
-      <c r="AK6" s="26"/>
-      <c r="AM6" s="26"/>
-      <c r="AN6" s="26"/>
-      <c r="AR6" s="26"/>
-      <c r="AS6" s="26"/>
-      <c r="AW6" s="26"/>
-      <c r="AX6" s="26"/>
-      <c r="BB6" s="26"/>
-      <c r="BC6" s="26"/>
-      <c r="BE6" s="26"/>
-      <c r="BF6" s="26"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="25"/>
+      <c r="P6" s="25"/>
+      <c r="Q6" s="25"/>
+      <c r="U6" s="25"/>
+      <c r="V6" s="25"/>
+      <c r="AB6" s="25"/>
+      <c r="AC6" s="25"/>
+      <c r="AE6" s="25"/>
+      <c r="AF6" s="25"/>
+      <c r="AJ6" s="25"/>
+      <c r="AK6" s="25"/>
+      <c r="AM6" s="25"/>
+      <c r="AN6" s="25"/>
+      <c r="AR6" s="25"/>
+      <c r="AS6" s="25"/>
+      <c r="AW6" s="25"/>
+      <c r="AX6" s="25"/>
+      <c r="BB6" s="25"/>
+      <c r="BC6" s="25"/>
+      <c r="BE6" s="25"/>
+      <c r="BF6" s="25"/>
     </row>
     <row r="7" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
@@ -1502,42 +1944,45 @@
         <f t="shared" ref="G7:G23" si="0">SUM(D7,E7,F7)</f>
         <v>30371000</v>
       </c>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26"/>
-      <c r="N7" s="26"/>
-      <c r="O7" s="26"/>
-      <c r="Q7" s="26"/>
-      <c r="R7" s="26"/>
-      <c r="S7" s="26"/>
-      <c r="T7" s="26"/>
-      <c r="V7" s="26"/>
-      <c r="W7" s="26"/>
-      <c r="X7" s="26"/>
-      <c r="Y7" s="26"/>
-      <c r="Z7" s="26"/>
-      <c r="AA7" s="26"/>
-      <c r="AC7" s="26"/>
-      <c r="AD7" s="26"/>
-      <c r="AF7" s="26"/>
-      <c r="AG7" s="26"/>
-      <c r="AH7" s="26"/>
-      <c r="AI7" s="26"/>
-      <c r="AK7" s="26"/>
-      <c r="AL7" s="26"/>
-      <c r="AN7" s="26"/>
-      <c r="AO7" s="26"/>
-      <c r="AP7" s="26"/>
-      <c r="AQ7" s="26"/>
-      <c r="AS7" s="26"/>
-      <c r="AT7" s="26"/>
-      <c r="AU7" s="26"/>
-      <c r="AV7" s="26"/>
-      <c r="AX7" s="26"/>
-      <c r="AY7" s="26"/>
-      <c r="AZ7" s="26"/>
-      <c r="BA7" s="26"/>
-      <c r="BC7" s="26"/>
-      <c r="BD7" s="26"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
+      <c r="Q7" s="25"/>
+      <c r="R7" s="25"/>
+      <c r="S7" s="25"/>
+      <c r="T7" s="25"/>
+      <c r="V7" s="25"/>
+      <c r="W7" s="25"/>
+      <c r="X7" s="25"/>
+      <c r="Y7" s="25"/>
+      <c r="Z7" s="25"/>
+      <c r="AA7" s="25"/>
+      <c r="AC7" s="25"/>
+      <c r="AD7" s="25"/>
+      <c r="AF7" s="25"/>
+      <c r="AG7" s="25"/>
+      <c r="AH7" s="25"/>
+      <c r="AI7" s="25"/>
+      <c r="AK7" s="25"/>
+      <c r="AL7" s="25"/>
+      <c r="AN7" s="25"/>
+      <c r="AO7" s="25"/>
+      <c r="AP7" s="25"/>
+      <c r="AQ7" s="25"/>
+      <c r="AS7" s="25"/>
+      <c r="AT7" s="25"/>
+      <c r="AU7" s="25"/>
+      <c r="AV7" s="25"/>
+      <c r="AX7" s="25"/>
+      <c r="AY7" s="25"/>
+      <c r="AZ7" s="25"/>
+      <c r="BA7" s="25"/>
+      <c r="BC7" s="25"/>
+      <c r="BD7" s="25"/>
     </row>
     <row r="8" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
@@ -1562,24 +2007,27 @@
         <f t="shared" si="0"/>
         <v>30391000</v>
       </c>
-      <c r="L8" s="26"/>
-      <c r="N8" s="26"/>
-      <c r="Q8" s="26"/>
-      <c r="S8" s="26"/>
-      <c r="V8" s="26"/>
-      <c r="X8" s="26"/>
-      <c r="Z8" s="26"/>
-      <c r="AC8" s="26"/>
-      <c r="AF8" s="26"/>
-      <c r="AH8" s="26"/>
-      <c r="AK8" s="26"/>
-      <c r="AN8" s="26"/>
-      <c r="AP8" s="26"/>
-      <c r="AS8" s="26"/>
-      <c r="AU8" s="26"/>
-      <c r="AX8" s="26"/>
-      <c r="AZ8" s="26"/>
-      <c r="BC8" s="26"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="25"/>
+      <c r="N8" s="25"/>
+      <c r="Q8" s="25"/>
+      <c r="S8" s="25"/>
+      <c r="V8" s="25"/>
+      <c r="X8" s="25"/>
+      <c r="Z8" s="25"/>
+      <c r="AC8" s="25"/>
+      <c r="AF8" s="25"/>
+      <c r="AH8" s="25"/>
+      <c r="AK8" s="25"/>
+      <c r="AN8" s="25"/>
+      <c r="AP8" s="25"/>
+      <c r="AS8" s="25"/>
+      <c r="AU8" s="25"/>
+      <c r="AX8" s="25"/>
+      <c r="AZ8" s="25"/>
+      <c r="BC8" s="25"/>
     </row>
     <row r="9" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
@@ -1604,54 +2052,56 @@
         <f t="shared" si="0"/>
         <v>30080450</v>
       </c>
-      <c r="K9" s="24"/>
-      <c r="L9" s="25"/>
-      <c r="M9" s="25"/>
-      <c r="N9" s="25"/>
-      <c r="O9" s="25"/>
-      <c r="P9" s="25"/>
-      <c r="Q9" s="25"/>
-      <c r="R9" s="25"/>
-      <c r="S9" s="25"/>
-      <c r="T9" s="25"/>
-      <c r="U9" s="25"/>
-      <c r="V9" s="25"/>
-      <c r="W9" s="25"/>
-      <c r="X9" s="25"/>
-      <c r="Y9" s="25"/>
-      <c r="Z9" s="25"/>
-      <c r="AA9" s="25"/>
-      <c r="AB9" s="25"/>
-      <c r="AC9" s="25"/>
-      <c r="AD9" s="25"/>
-      <c r="AE9" s="25"/>
-      <c r="AF9" s="25"/>
-      <c r="AG9" s="25"/>
-      <c r="AH9" s="25"/>
-      <c r="AI9" s="25"/>
-      <c r="AJ9" s="25"/>
-      <c r="AK9" s="25"/>
-      <c r="AL9" s="25"/>
-      <c r="AM9" s="25"/>
-      <c r="AN9" s="25"/>
-      <c r="AO9" s="25"/>
-      <c r="AP9" s="25"/>
-      <c r="AQ9" s="25"/>
-      <c r="AR9" s="25"/>
-      <c r="AS9" s="25"/>
-      <c r="AT9" s="25"/>
-      <c r="AU9" s="25"/>
-      <c r="AV9" s="25"/>
-      <c r="AW9" s="25"/>
-      <c r="AX9" s="25"/>
-      <c r="AY9" s="25"/>
-      <c r="AZ9" s="25"/>
-      <c r="BA9" s="25"/>
-      <c r="BB9" s="25"/>
-      <c r="BC9" s="25"/>
-      <c r="BD9" s="25"/>
-      <c r="BE9" s="25"/>
-      <c r="BF9" s="25"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="24"/>
+      <c r="M9" s="24"/>
+      <c r="N9" s="24"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="24"/>
+      <c r="R9" s="24"/>
+      <c r="S9" s="24"/>
+      <c r="T9" s="24"/>
+      <c r="U9" s="24"/>
+      <c r="V9" s="24"/>
+      <c r="W9" s="24"/>
+      <c r="X9" s="24"/>
+      <c r="Y9" s="24"/>
+      <c r="Z9" s="24"/>
+      <c r="AA9" s="24"/>
+      <c r="AB9" s="24"/>
+      <c r="AC9" s="24"/>
+      <c r="AD9" s="24"/>
+      <c r="AE9" s="24"/>
+      <c r="AF9" s="24"/>
+      <c r="AG9" s="24"/>
+      <c r="AH9" s="24"/>
+      <c r="AI9" s="24"/>
+      <c r="AJ9" s="24"/>
+      <c r="AK9" s="24"/>
+      <c r="AL9" s="24"/>
+      <c r="AM9" s="24"/>
+      <c r="AN9" s="24"/>
+      <c r="AO9" s="24"/>
+      <c r="AP9" s="24"/>
+      <c r="AQ9" s="24"/>
+      <c r="AR9" s="24"/>
+      <c r="AS9" s="24"/>
+      <c r="AT9" s="24"/>
+      <c r="AU9" s="24"/>
+      <c r="AV9" s="24"/>
+      <c r="AW9" s="24"/>
+      <c r="AX9" s="24"/>
+      <c r="AY9" s="24"/>
+      <c r="AZ9" s="24"/>
+      <c r="BA9" s="24"/>
+      <c r="BB9" s="24"/>
+      <c r="BC9" s="24"/>
+      <c r="BD9" s="24"/>
+      <c r="BE9" s="24"/>
+      <c r="BF9" s="24"/>
     </row>
     <row r="10" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -1676,54 +2126,56 @@
         <f t="shared" si="0"/>
         <v>30377100</v>
       </c>
-      <c r="K10" s="24"/>
-      <c r="L10" s="25"/>
-      <c r="M10" s="25"/>
-      <c r="N10" s="25"/>
-      <c r="O10" s="25"/>
-      <c r="P10" s="25"/>
-      <c r="Q10" s="25"/>
-      <c r="R10" s="25"/>
-      <c r="S10" s="25"/>
-      <c r="T10" s="25"/>
-      <c r="U10" s="25"/>
-      <c r="V10" s="25"/>
-      <c r="W10" s="25"/>
-      <c r="X10" s="25"/>
-      <c r="Y10" s="25"/>
-      <c r="Z10" s="25"/>
-      <c r="AA10" s="25"/>
-      <c r="AB10" s="25"/>
-      <c r="AC10" s="25"/>
-      <c r="AD10" s="25"/>
-      <c r="AE10" s="25"/>
-      <c r="AF10" s="25"/>
-      <c r="AG10" s="25"/>
-      <c r="AH10" s="25"/>
-      <c r="AI10" s="25"/>
-      <c r="AJ10" s="25"/>
-      <c r="AK10" s="25"/>
-      <c r="AL10" s="25"/>
-      <c r="AM10" s="25"/>
-      <c r="AN10" s="25"/>
-      <c r="AO10" s="25"/>
-      <c r="AP10" s="25"/>
-      <c r="AQ10" s="25"/>
-      <c r="AR10" s="25"/>
-      <c r="AS10" s="25"/>
-      <c r="AT10" s="25"/>
-      <c r="AU10" s="25"/>
-      <c r="AV10" s="25"/>
-      <c r="AW10" s="25"/>
-      <c r="AX10" s="25"/>
-      <c r="AY10" s="25"/>
-      <c r="AZ10" s="25"/>
-      <c r="BA10" s="25"/>
-      <c r="BB10" s="25"/>
-      <c r="BC10" s="25"/>
-      <c r="BD10" s="25"/>
-      <c r="BE10" s="25"/>
-      <c r="BF10" s="25"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="30"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="24"/>
+      <c r="M10" s="24"/>
+      <c r="N10" s="24"/>
+      <c r="O10" s="24"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="24"/>
+      <c r="R10" s="24"/>
+      <c r="S10" s="24"/>
+      <c r="T10" s="24"/>
+      <c r="U10" s="24"/>
+      <c r="V10" s="24"/>
+      <c r="W10" s="24"/>
+      <c r="X10" s="24"/>
+      <c r="Y10" s="24"/>
+      <c r="Z10" s="24"/>
+      <c r="AA10" s="24"/>
+      <c r="AB10" s="24"/>
+      <c r="AC10" s="24"/>
+      <c r="AD10" s="24"/>
+      <c r="AE10" s="24"/>
+      <c r="AF10" s="24"/>
+      <c r="AG10" s="24"/>
+      <c r="AH10" s="24"/>
+      <c r="AI10" s="24"/>
+      <c r="AJ10" s="24"/>
+      <c r="AK10" s="24"/>
+      <c r="AL10" s="24"/>
+      <c r="AM10" s="24"/>
+      <c r="AN10" s="24"/>
+      <c r="AO10" s="24"/>
+      <c r="AP10" s="24"/>
+      <c r="AQ10" s="24"/>
+      <c r="AR10" s="24"/>
+      <c r="AS10" s="24"/>
+      <c r="AT10" s="24"/>
+      <c r="AU10" s="24"/>
+      <c r="AV10" s="24"/>
+      <c r="AW10" s="24"/>
+      <c r="AX10" s="24"/>
+      <c r="AY10" s="24"/>
+      <c r="AZ10" s="24"/>
+      <c r="BA10" s="24"/>
+      <c r="BB10" s="24"/>
+      <c r="BC10" s="24"/>
+      <c r="BD10" s="24"/>
+      <c r="BE10" s="24"/>
+      <c r="BF10" s="24"/>
     </row>
     <row r="11" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -1748,54 +2200,56 @@
         <f t="shared" si="0"/>
         <v>30047790</v>
       </c>
-      <c r="K11" s="24"/>
-      <c r="L11" s="25"/>
-      <c r="M11" s="25"/>
-      <c r="N11" s="25"/>
-      <c r="O11" s="25"/>
-      <c r="P11" s="25"/>
-      <c r="Q11" s="25"/>
-      <c r="R11" s="25"/>
-      <c r="S11" s="25"/>
-      <c r="T11" s="25"/>
-      <c r="U11" s="25"/>
-      <c r="V11" s="25"/>
-      <c r="W11" s="25"/>
-      <c r="X11" s="25"/>
-      <c r="Y11" s="25"/>
-      <c r="Z11" s="25"/>
-      <c r="AA11" s="25"/>
-      <c r="AB11" s="25"/>
-      <c r="AC11" s="25"/>
-      <c r="AD11" s="25"/>
-      <c r="AE11" s="25"/>
-      <c r="AF11" s="25"/>
-      <c r="AG11" s="25"/>
-      <c r="AH11" s="25"/>
-      <c r="AI11" s="25"/>
-      <c r="AJ11" s="25"/>
-      <c r="AK11" s="25"/>
-      <c r="AL11" s="25"/>
-      <c r="AM11" s="25"/>
-      <c r="AN11" s="25"/>
-      <c r="AO11" s="25"/>
-      <c r="AP11" s="25"/>
-      <c r="AQ11" s="25"/>
-      <c r="AR11" s="25"/>
-      <c r="AS11" s="25"/>
-      <c r="AT11" s="25"/>
-      <c r="AU11" s="25"/>
-      <c r="AV11" s="25"/>
-      <c r="AW11" s="25"/>
-      <c r="AX11" s="25"/>
-      <c r="AY11" s="25"/>
-      <c r="AZ11" s="25"/>
-      <c r="BA11" s="25"/>
-      <c r="BB11" s="25"/>
-      <c r="BC11" s="25"/>
-      <c r="BD11" s="25"/>
-      <c r="BE11" s="25"/>
-      <c r="BF11" s="25"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="31"/>
+      <c r="L11" s="24"/>
+      <c r="M11" s="24"/>
+      <c r="N11" s="24"/>
+      <c r="O11" s="24"/>
+      <c r="P11" s="24"/>
+      <c r="Q11" s="24"/>
+      <c r="R11" s="24"/>
+      <c r="S11" s="24"/>
+      <c r="T11" s="24"/>
+      <c r="U11" s="24"/>
+      <c r="V11" s="24"/>
+      <c r="W11" s="24"/>
+      <c r="X11" s="24"/>
+      <c r="Y11" s="24"/>
+      <c r="Z11" s="24"/>
+      <c r="AA11" s="24"/>
+      <c r="AB11" s="24"/>
+      <c r="AC11" s="24"/>
+      <c r="AD11" s="24"/>
+      <c r="AE11" s="24"/>
+      <c r="AF11" s="24"/>
+      <c r="AG11" s="24"/>
+      <c r="AH11" s="24"/>
+      <c r="AI11" s="24"/>
+      <c r="AJ11" s="24"/>
+      <c r="AK11" s="24"/>
+      <c r="AL11" s="24"/>
+      <c r="AM11" s="24"/>
+      <c r="AN11" s="24"/>
+      <c r="AO11" s="24"/>
+      <c r="AP11" s="24"/>
+      <c r="AQ11" s="24"/>
+      <c r="AR11" s="24"/>
+      <c r="AS11" s="24"/>
+      <c r="AT11" s="24"/>
+      <c r="AU11" s="24"/>
+      <c r="AV11" s="24"/>
+      <c r="AW11" s="24"/>
+      <c r="AX11" s="24"/>
+      <c r="AY11" s="24"/>
+      <c r="AZ11" s="24"/>
+      <c r="BA11" s="24"/>
+      <c r="BB11" s="24"/>
+      <c r="BC11" s="24"/>
+      <c r="BD11" s="24"/>
+      <c r="BE11" s="24"/>
+      <c r="BF11" s="24"/>
     </row>
     <row r="12" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
@@ -1820,54 +2274,56 @@
         <f t="shared" si="0"/>
         <v>30757000</v>
       </c>
-      <c r="K12" s="24"/>
-      <c r="L12" s="25"/>
-      <c r="M12" s="25"/>
-      <c r="N12" s="25"/>
-      <c r="O12" s="25"/>
-      <c r="P12" s="25"/>
-      <c r="Q12" s="25"/>
-      <c r="R12" s="25"/>
-      <c r="S12" s="25"/>
-      <c r="T12" s="25"/>
-      <c r="U12" s="25"/>
-      <c r="V12" s="25"/>
-      <c r="W12" s="25"/>
-      <c r="X12" s="25"/>
-      <c r="Y12" s="25"/>
-      <c r="Z12" s="25"/>
-      <c r="AA12" s="25"/>
-      <c r="AB12" s="25"/>
-      <c r="AC12" s="25"/>
-      <c r="AD12" s="25"/>
-      <c r="AE12" s="25"/>
-      <c r="AF12" s="25"/>
-      <c r="AG12" s="25"/>
-      <c r="AH12" s="25"/>
-      <c r="AI12" s="25"/>
-      <c r="AJ12" s="25"/>
-      <c r="AK12" s="25"/>
-      <c r="AL12" s="25"/>
-      <c r="AM12" s="25"/>
-      <c r="AN12" s="25"/>
-      <c r="AO12" s="25"/>
-      <c r="AP12" s="25"/>
-      <c r="AQ12" s="25"/>
-      <c r="AR12" s="25"/>
-      <c r="AS12" s="25"/>
-      <c r="AT12" s="25"/>
-      <c r="AU12" s="25"/>
-      <c r="AV12" s="25"/>
-      <c r="AW12" s="25"/>
-      <c r="AX12" s="25"/>
-      <c r="AY12" s="25"/>
-      <c r="AZ12" s="25"/>
-      <c r="BA12" s="25"/>
-      <c r="BB12" s="25"/>
-      <c r="BC12" s="25"/>
-      <c r="BD12" s="25"/>
-      <c r="BE12" s="25"/>
-      <c r="BF12" s="25"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="24"/>
+      <c r="M12" s="24"/>
+      <c r="N12" s="24"/>
+      <c r="O12" s="24"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="24"/>
+      <c r="R12" s="24"/>
+      <c r="S12" s="24"/>
+      <c r="T12" s="24"/>
+      <c r="U12" s="24"/>
+      <c r="V12" s="24"/>
+      <c r="W12" s="24"/>
+      <c r="X12" s="24"/>
+      <c r="Y12" s="24"/>
+      <c r="Z12" s="24"/>
+      <c r="AA12" s="24"/>
+      <c r="AB12" s="24"/>
+      <c r="AC12" s="24"/>
+      <c r="AD12" s="24"/>
+      <c r="AE12" s="24"/>
+      <c r="AF12" s="24"/>
+      <c r="AG12" s="24"/>
+      <c r="AH12" s="24"/>
+      <c r="AI12" s="24"/>
+      <c r="AJ12" s="24"/>
+      <c r="AK12" s="24"/>
+      <c r="AL12" s="24"/>
+      <c r="AM12" s="24"/>
+      <c r="AN12" s="24"/>
+      <c r="AO12" s="24"/>
+      <c r="AP12" s="24"/>
+      <c r="AQ12" s="24"/>
+      <c r="AR12" s="24"/>
+      <c r="AS12" s="24"/>
+      <c r="AT12" s="24"/>
+      <c r="AU12" s="24"/>
+      <c r="AV12" s="24"/>
+      <c r="AW12" s="24"/>
+      <c r="AX12" s="24"/>
+      <c r="AY12" s="24"/>
+      <c r="AZ12" s="24"/>
+      <c r="BA12" s="24"/>
+      <c r="BB12" s="24"/>
+      <c r="BC12" s="24"/>
+      <c r="BD12" s="24"/>
+      <c r="BE12" s="24"/>
+      <c r="BF12" s="24"/>
     </row>
     <row r="13" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
@@ -1892,54 +2348,56 @@
         <f t="shared" si="0"/>
         <v>30019600</v>
       </c>
-      <c r="K13" s="24"/>
-      <c r="L13" s="25"/>
-      <c r="M13" s="25"/>
-      <c r="N13" s="25"/>
-      <c r="O13" s="25"/>
-      <c r="P13" s="25"/>
-      <c r="Q13" s="25"/>
-      <c r="R13" s="25"/>
-      <c r="S13" s="25"/>
-      <c r="T13" s="25"/>
-      <c r="U13" s="25"/>
-      <c r="V13" s="25"/>
-      <c r="W13" s="25"/>
-      <c r="X13" s="25"/>
-      <c r="Y13" s="25"/>
-      <c r="Z13" s="25"/>
-      <c r="AA13" s="25"/>
-      <c r="AB13" s="25"/>
-      <c r="AC13" s="25"/>
-      <c r="AD13" s="25"/>
-      <c r="AE13" s="25"/>
-      <c r="AF13" s="25"/>
-      <c r="AG13" s="25"/>
-      <c r="AH13" s="25"/>
-      <c r="AI13" s="25"/>
-      <c r="AJ13" s="25"/>
-      <c r="AK13" s="25"/>
-      <c r="AL13" s="25"/>
-      <c r="AM13" s="25"/>
-      <c r="AN13" s="25"/>
-      <c r="AO13" s="25"/>
-      <c r="AP13" s="25"/>
-      <c r="AQ13" s="25"/>
-      <c r="AR13" s="25"/>
-      <c r="AS13" s="25"/>
-      <c r="AT13" s="25"/>
-      <c r="AU13" s="25"/>
-      <c r="AV13" s="25"/>
-      <c r="AW13" s="25"/>
-      <c r="AX13" s="25"/>
-      <c r="AY13" s="25"/>
-      <c r="AZ13" s="25"/>
-      <c r="BA13" s="25"/>
-      <c r="BB13" s="25"/>
-      <c r="BC13" s="25"/>
-      <c r="BD13" s="25"/>
-      <c r="BE13" s="25"/>
-      <c r="BF13" s="25"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="30"/>
+      <c r="K13" s="31"/>
+      <c r="L13" s="24"/>
+      <c r="M13" s="24"/>
+      <c r="N13" s="24"/>
+      <c r="O13" s="24"/>
+      <c r="P13" s="24"/>
+      <c r="Q13" s="24"/>
+      <c r="R13" s="24"/>
+      <c r="S13" s="24"/>
+      <c r="T13" s="24"/>
+      <c r="U13" s="24"/>
+      <c r="V13" s="24"/>
+      <c r="W13" s="24"/>
+      <c r="X13" s="24"/>
+      <c r="Y13" s="24"/>
+      <c r="Z13" s="24"/>
+      <c r="AA13" s="24"/>
+      <c r="AB13" s="24"/>
+      <c r="AC13" s="24"/>
+      <c r="AD13" s="24"/>
+      <c r="AE13" s="24"/>
+      <c r="AF13" s="24"/>
+      <c r="AG13" s="24"/>
+      <c r="AH13" s="24"/>
+      <c r="AI13" s="24"/>
+      <c r="AJ13" s="24"/>
+      <c r="AK13" s="24"/>
+      <c r="AL13" s="24"/>
+      <c r="AM13" s="24"/>
+      <c r="AN13" s="24"/>
+      <c r="AO13" s="24"/>
+      <c r="AP13" s="24"/>
+      <c r="AQ13" s="24"/>
+      <c r="AR13" s="24"/>
+      <c r="AS13" s="24"/>
+      <c r="AT13" s="24"/>
+      <c r="AU13" s="24"/>
+      <c r="AV13" s="24"/>
+      <c r="AW13" s="24"/>
+      <c r="AX13" s="24"/>
+      <c r="AY13" s="24"/>
+      <c r="AZ13" s="24"/>
+      <c r="BA13" s="24"/>
+      <c r="BB13" s="24"/>
+      <c r="BC13" s="24"/>
+      <c r="BD13" s="24"/>
+      <c r="BE13" s="24"/>
+      <c r="BF13" s="24"/>
     </row>
     <row r="14" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
@@ -1964,54 +2422,56 @@
         <f t="shared" si="0"/>
         <v>30039740</v>
       </c>
-      <c r="K14" s="24"/>
-      <c r="L14" s="25"/>
-      <c r="M14" s="25"/>
-      <c r="N14" s="25"/>
-      <c r="O14" s="25"/>
-      <c r="P14" s="25"/>
-      <c r="Q14" s="25"/>
-      <c r="R14" s="25"/>
-      <c r="S14" s="25"/>
-      <c r="T14" s="25"/>
-      <c r="U14" s="25"/>
-      <c r="V14" s="25"/>
-      <c r="W14" s="25"/>
-      <c r="X14" s="25"/>
-      <c r="Y14" s="25"/>
-      <c r="Z14" s="25"/>
-      <c r="AA14" s="25"/>
-      <c r="AB14" s="25"/>
-      <c r="AC14" s="25"/>
-      <c r="AD14" s="25"/>
-      <c r="AE14" s="25"/>
-      <c r="AF14" s="25"/>
-      <c r="AG14" s="25"/>
-      <c r="AH14" s="25"/>
-      <c r="AI14" s="25"/>
-      <c r="AJ14" s="25"/>
-      <c r="AK14" s="25"/>
-      <c r="AL14" s="25"/>
-      <c r="AM14" s="25"/>
-      <c r="AN14" s="25"/>
-      <c r="AO14" s="25"/>
-      <c r="AP14" s="25"/>
-      <c r="AQ14" s="25"/>
-      <c r="AR14" s="25"/>
-      <c r="AS14" s="25"/>
-      <c r="AT14" s="25"/>
-      <c r="AU14" s="25"/>
-      <c r="AV14" s="25"/>
-      <c r="AW14" s="25"/>
-      <c r="AX14" s="25"/>
-      <c r="AY14" s="25"/>
-      <c r="AZ14" s="25"/>
-      <c r="BA14" s="25"/>
-      <c r="BB14" s="25"/>
-      <c r="BC14" s="25"/>
-      <c r="BD14" s="25"/>
-      <c r="BE14" s="25"/>
-      <c r="BF14" s="25"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="31"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="24"/>
+      <c r="O14" s="24"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="24"/>
+      <c r="R14" s="24"/>
+      <c r="S14" s="24"/>
+      <c r="T14" s="24"/>
+      <c r="U14" s="24"/>
+      <c r="V14" s="24"/>
+      <c r="W14" s="24"/>
+      <c r="X14" s="24"/>
+      <c r="Y14" s="24"/>
+      <c r="Z14" s="24"/>
+      <c r="AA14" s="24"/>
+      <c r="AB14" s="24"/>
+      <c r="AC14" s="24"/>
+      <c r="AD14" s="24"/>
+      <c r="AE14" s="24"/>
+      <c r="AF14" s="24"/>
+      <c r="AG14" s="24"/>
+      <c r="AH14" s="24"/>
+      <c r="AI14" s="24"/>
+      <c r="AJ14" s="24"/>
+      <c r="AK14" s="24"/>
+      <c r="AL14" s="24"/>
+      <c r="AM14" s="24"/>
+      <c r="AN14" s="24"/>
+      <c r="AO14" s="24"/>
+      <c r="AP14" s="24"/>
+      <c r="AQ14" s="24"/>
+      <c r="AR14" s="24"/>
+      <c r="AS14" s="24"/>
+      <c r="AT14" s="24"/>
+      <c r="AU14" s="24"/>
+      <c r="AV14" s="24"/>
+      <c r="AW14" s="24"/>
+      <c r="AX14" s="24"/>
+      <c r="AY14" s="24"/>
+      <c r="AZ14" s="24"/>
+      <c r="BA14" s="24"/>
+      <c r="BB14" s="24"/>
+      <c r="BC14" s="24"/>
+      <c r="BD14" s="24"/>
+      <c r="BE14" s="24"/>
+      <c r="BF14" s="24"/>
     </row>
     <row r="15" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -2036,54 +2496,56 @@
         <f t="shared" si="0"/>
         <v>34901400</v>
       </c>
-      <c r="K15" s="24"/>
-      <c r="L15" s="25"/>
-      <c r="M15" s="25"/>
-      <c r="N15" s="25"/>
-      <c r="O15" s="25"/>
-      <c r="P15" s="25"/>
-      <c r="Q15" s="25"/>
-      <c r="R15" s="25"/>
-      <c r="S15" s="25"/>
-      <c r="T15" s="25"/>
-      <c r="U15" s="25"/>
-      <c r="V15" s="25"/>
-      <c r="W15" s="25"/>
-      <c r="X15" s="25"/>
-      <c r="Y15" s="25"/>
-      <c r="Z15" s="25"/>
-      <c r="AA15" s="25"/>
-      <c r="AB15" s="25"/>
-      <c r="AC15" s="25"/>
-      <c r="AD15" s="25"/>
-      <c r="AE15" s="25"/>
-      <c r="AF15" s="25"/>
-      <c r="AG15" s="25"/>
-      <c r="AH15" s="25"/>
-      <c r="AI15" s="25"/>
-      <c r="AJ15" s="25"/>
-      <c r="AK15" s="25"/>
-      <c r="AL15" s="25"/>
-      <c r="AM15" s="25"/>
-      <c r="AN15" s="25"/>
-      <c r="AO15" s="25"/>
-      <c r="AP15" s="25"/>
-      <c r="AQ15" s="25"/>
-      <c r="AR15" s="25"/>
-      <c r="AS15" s="25"/>
-      <c r="AT15" s="25"/>
-      <c r="AU15" s="25"/>
-      <c r="AV15" s="25"/>
-      <c r="AW15" s="25"/>
-      <c r="AX15" s="25"/>
-      <c r="AY15" s="25"/>
-      <c r="AZ15" s="25"/>
-      <c r="BA15" s="25"/>
-      <c r="BB15" s="25"/>
-      <c r="BC15" s="25"/>
-      <c r="BD15" s="25"/>
-      <c r="BE15" s="25"/>
-      <c r="BF15" s="25"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="31"/>
+      <c r="L15" s="24"/>
+      <c r="M15" s="24"/>
+      <c r="N15" s="24"/>
+      <c r="O15" s="24"/>
+      <c r="P15" s="24"/>
+      <c r="Q15" s="24"/>
+      <c r="R15" s="24"/>
+      <c r="S15" s="24"/>
+      <c r="T15" s="24"/>
+      <c r="U15" s="24"/>
+      <c r="V15" s="24"/>
+      <c r="W15" s="24"/>
+      <c r="X15" s="24"/>
+      <c r="Y15" s="24"/>
+      <c r="Z15" s="24"/>
+      <c r="AA15" s="24"/>
+      <c r="AB15" s="24"/>
+      <c r="AC15" s="24"/>
+      <c r="AD15" s="24"/>
+      <c r="AE15" s="24"/>
+      <c r="AF15" s="24"/>
+      <c r="AG15" s="24"/>
+      <c r="AH15" s="24"/>
+      <c r="AI15" s="24"/>
+      <c r="AJ15" s="24"/>
+      <c r="AK15" s="24"/>
+      <c r="AL15" s="24"/>
+      <c r="AM15" s="24"/>
+      <c r="AN15" s="24"/>
+      <c r="AO15" s="24"/>
+      <c r="AP15" s="24"/>
+      <c r="AQ15" s="24"/>
+      <c r="AR15" s="24"/>
+      <c r="AS15" s="24"/>
+      <c r="AT15" s="24"/>
+      <c r="AU15" s="24"/>
+      <c r="AV15" s="24"/>
+      <c r="AW15" s="24"/>
+      <c r="AX15" s="24"/>
+      <c r="AY15" s="24"/>
+      <c r="AZ15" s="24"/>
+      <c r="BA15" s="24"/>
+      <c r="BB15" s="24"/>
+      <c r="BC15" s="24"/>
+      <c r="BD15" s="24"/>
+      <c r="BE15" s="24"/>
+      <c r="BF15" s="24"/>
     </row>
     <row r="16" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
@@ -2108,8 +2570,11 @@
         <f t="shared" si="0"/>
         <v>30081400</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I16" s="29"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="31"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
         <v>48</v>
       </c>
@@ -2132,8 +2597,11 @@
         <f t="shared" si="0"/>
         <v>30168000</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I17" s="29"/>
+      <c r="J17" s="30"/>
+      <c r="K17" s="31"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="18" t="s">
         <v>11</v>
       </c>
@@ -2156,8 +2624,11 @@
         <f t="shared" si="0"/>
         <v>30098700</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I18" s="29"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="31"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
         <v>49</v>
       </c>
@@ -2180,8 +2651,11 @@
         <f t="shared" si="0"/>
         <v>30038340</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I19" s="29"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="31"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
         <v>50</v>
       </c>
@@ -2204,8 +2678,11 @@
         <f t="shared" si="0"/>
         <v>30369000</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I20" s="29"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="31"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="18" t="s">
         <v>51</v>
       </c>
@@ -2228,8 +2705,11 @@
         <f t="shared" si="0"/>
         <v>30026450</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I21" s="29"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="31"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="18" t="s">
         <v>52</v>
       </c>
@@ -2252,8 +2732,11 @@
         <f t="shared" si="0"/>
         <v>30703400</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I22" s="32"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="34"/>
+    </row>
+    <row r="23" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="19" t="s">
         <v>53</v>
       </c>
@@ -2279,7 +2762,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
